--- a/database/event/4889/event_4889_evp_summary.xlsx
+++ b/database/event/4889/event_4889_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>0.9959</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3002</v>
+        <v>1.2539</v>
       </c>
       <c r="E2" t="n">
         <v>4.2615</v>
@@ -548,7 +548,7 @@
         <v>0.9838</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2792</v>
+        <v>1.2332</v>
       </c>
       <c r="E3" t="n">
         <v>4.2096</v>
@@ -594,7 +594,7 @@
         <v>0.9304</v>
       </c>
       <c r="D4" t="n">
-        <v>1.187</v>
+        <v>1.1422</v>
       </c>
       <c r="E4" t="n">
         <v>3.9812</v>
@@ -640,7 +640,7 @@
         <v>0.8614000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0677</v>
+        <v>1.0246</v>
       </c>
       <c r="E5" t="n">
         <v>3.6859</v>
@@ -686,7 +686,7 @@
         <v>0.797</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9564</v>
+        <v>0.9147999999999999</v>
       </c>
       <c r="E6" t="n">
         <v>3.4104</v>
@@ -732,7 +732,7 @@
         <v>0.6108</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6344</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="E7" t="n">
         <v>2.6135</v>
@@ -778,7 +778,7 @@
         <v>0.3654</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2102</v>
+        <v>0.1789</v>
       </c>
       <c r="E8" t="n">
         <v>1.5634</v>
@@ -824,7 +824,7 @@
         <v>0.2133</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0526</v>
+        <v>-0.0803</v>
       </c>
       <c r="E9" t="n">
         <v>0.9127999999999999</v>
@@ -870,7 +870,7 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2751</v>
+        <v>-0.2997</v>
       </c>
       <c r="E10" t="n">
         <v>0.362</v>
@@ -916,7 +916,7 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.302</v>
+        <v>-0.3262</v>
       </c>
       <c r="E11" t="n">
         <v>0.2955</v>
@@ -962,7 +962,7 @@
         <v>0.0357</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3596</v>
+        <v>-0.383</v>
       </c>
       <c r="E12" t="n">
         <v>0.1528</v>
@@ -1008,7 +1008,7 @@
         <v>0.0151</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3953</v>
+        <v>-0.4182</v>
       </c>
       <c r="E13" t="n">
         <v>0.0646</v>
@@ -1054,7 +1054,7 @@
         <v>-0.0581</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5218</v>
+        <v>-0.543</v>
       </c>
       <c r="E14" t="n">
         <v>-0.2487</v>
@@ -1100,7 +1100,7 @@
         <v>-0.06619999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.5568</v>
       </c>
       <c r="E15" t="n">
         <v>-0.2833</v>
@@ -1146,7 +1146,7 @@
         <v>-0.1015</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5968</v>
+        <v>-0.6169</v>
       </c>
       <c r="E16" t="n">
         <v>-0.4343</v>
@@ -1192,7 +1192,7 @@
         <v>-0.1205</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6297</v>
+        <v>-0.6494</v>
       </c>
       <c r="E17" t="n">
         <v>-0.5158</v>
@@ -1238,7 +1238,7 @@
         <v>-0.3025</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9442</v>
+        <v>-0.9596</v>
       </c>
       <c r="E18" t="n">
         <v>-1.2943</v>
@@ -1284,7 +1284,7 @@
         <v>-0.3333</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-1.0121</v>
       </c>
       <c r="E19" t="n">
         <v>-1.4262</v>
@@ -1330,7 +1330,7 @@
         <v>-0.3871</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0905</v>
+        <v>-1.1038</v>
       </c>
       <c r="E20" t="n">
         <v>-1.6564</v>
@@ -1376,7 +1376,7 @@
         <v>-0.6783</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5938</v>
+        <v>-1.6001</v>
       </c>
       <c r="E21" t="n">
         <v>-2.9022</v>

--- a/database/event/4889/event_4889_evp_summary.xlsx
+++ b/database/event/4889/event_4889_evp_summary.xlsx
@@ -492,185 +492,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.2615</v>
+        <v>4.1577</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9959</v>
+        <v>0.9717</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2539</v>
+        <v>1.239</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2615</v>
+        <v>4.1577</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3299</v>
+        <v>2.5016</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9316</v>
+        <v>1.6561</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3299</v>
+        <v>3.3276</v>
       </c>
       <c r="I2" t="n">
-        <v>2.699</v>
+        <v>1.7302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9316</v>
+        <v>1.6561</v>
       </c>
       <c r="K2" t="n">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="L2" t="n">
         <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6306</v>
+        <v>3.3863</v>
       </c>
       <c r="N2" t="n">
-        <v>251</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2096</v>
+        <v>4.0749</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9838</v>
+        <v>0.9523</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2332</v>
+        <v>1.2016</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2096</v>
+        <v>4.0749</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8215</v>
+        <v>1.5549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3881</v>
+        <v>2.52</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8215</v>
+        <v>1.5549</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0975</v>
+        <v>0.8085</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3881</v>
+        <v>2.52</v>
       </c>
       <c r="K3" t="n">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="L3" t="n">
         <v>112</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4856</v>
+        <v>3.3285</v>
       </c>
       <c r="N3" t="n">
-        <v>251</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9812</v>
+        <v>4.0605</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9304</v>
+        <v>0.9489</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1422</v>
+        <v>1.1951</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9812</v>
+        <v>4.0605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.899</v>
+        <v>3.0049</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0821</v>
+        <v>1.0556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.899</v>
+        <v>5.1012</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7287</v>
+        <v>2.6524</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0821</v>
+        <v>1.0556</v>
       </c>
       <c r="K4" t="n">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="L4" t="n">
         <v>112</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8108</v>
+        <v>3.708</v>
       </c>
       <c r="N4" t="n">
-        <v>163</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6859</v>
+        <v>3.7615</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8791</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0246</v>
+        <v>1.0601</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6859</v>
+        <v>3.7615</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0944</v>
+        <v>3.3345</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5915</v>
+        <v>0.427</v>
       </c>
       <c r="H5" t="n">
-        <v>2.0944</v>
+        <v>6.2625</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6975</v>
+        <v>3.2562</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5915</v>
+        <v>0.427</v>
       </c>
       <c r="K5" t="n">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="L5" t="n">
         <v>112</v>
       </c>
       <c r="M5" t="n">
-        <v>3.289</v>
+        <v>3.6832</v>
       </c>
       <c r="N5" t="n">
-        <v>163</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4104</v>
+        <v>3.6892</v>
       </c>
       <c r="C6" t="n">
-        <v>0.797</v>
+        <v>0.8622</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9147999999999999</v>
+        <v>1.0275</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4104</v>
+        <v>3.6892</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2903</v>
+        <v>2.6373</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1201</v>
+        <v>1.0519</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2903</v>
+        <v>3.8057</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8564</v>
+        <v>1.9788</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1201</v>
+        <v>1.0519</v>
       </c>
       <c r="K6" t="n">
         <v>51</v>
@@ -713,7 +713,7 @@
         <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9765</v>
+        <v>3.0307</v>
       </c>
       <c r="N6" t="n">
         <v>163</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6135</v>
+        <v>3.339</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6108</v>
+        <v>0.7803</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.8694</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6135</v>
+        <v>3.339</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6516</v>
+        <v>2.3436</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9619</v>
+        <v>0.9954</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6516</v>
+        <v>2.7712</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3387</v>
+        <v>1.4409</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9619</v>
+        <v>0.9954</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -759,7 +759,7 @@
         <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3006</v>
+        <v>2.4363</v>
       </c>
       <c r="N7" t="n">
         <v>163</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.5634</v>
+        <v>1.3051</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3654</v>
+        <v>0.305</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1789</v>
+        <v>-0.0488</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5634</v>
+        <v>1.3051</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7968</v>
+        <v>0.356</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3602</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7968</v>
+        <v>0.356</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6458</v>
+        <v>0.1851</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3602</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>107</v>
@@ -805,7 +805,7 @@
         <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7144</v>
+        <v>1.1342</v>
       </c>
       <c r="N8" t="n">
         <v>159</v>
@@ -814,127 +814,127 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9127999999999999</v>
+        <v>1.1699</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2133</v>
+        <v>0.2734</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0803</v>
+        <v>-0.1099</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9127999999999999</v>
+        <v>1.1699</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1925</v>
+        <v>1.8409</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1053</v>
+        <v>-0.671</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1925</v>
+        <v>1.8409</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.156</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1053</v>
+        <v>-0.671</v>
       </c>
       <c r="K9" t="n">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9492999999999999</v>
+        <v>0.2862</v>
       </c>
       <c r="N9" t="n">
-        <v>159</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.362</v>
+        <v>1.0431</v>
       </c>
       <c r="C10" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.2438</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2997</v>
+        <v>-0.1671</v>
       </c>
       <c r="E10" t="n">
-        <v>0.362</v>
+        <v>1.0431</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2635</v>
+        <v>-0.7256</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0985</v>
+        <v>1.7687</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2635</v>
+        <v>-0.7256</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2136</v>
+        <v>-0.3773</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0985</v>
+        <v>1.7687</v>
       </c>
       <c r="K10" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="L10" t="n">
         <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3121</v>
+        <v>1.3914</v>
       </c>
       <c r="N10" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2955</v>
+        <v>0.9669</v>
       </c>
       <c r="C11" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.226</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3262</v>
+        <v>-0.2015</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2955</v>
+        <v>0.9669</v>
       </c>
       <c r="F11" t="n">
-        <v>0.265</v>
+        <v>0.7353</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0305</v>
+        <v>0.2316</v>
       </c>
       <c r="H11" t="n">
-        <v>0.265</v>
+        <v>0.7353</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2148</v>
+        <v>0.3823</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0305</v>
+        <v>0.2316</v>
       </c>
       <c r="K11" t="n">
         <v>83</v>
@@ -943,7 +943,7 @@
         <v>52</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2453</v>
+        <v>0.6139</v>
       </c>
       <c r="N11" t="n">
         <v>135</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1528</v>
+        <v>0.8262</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0357</v>
+        <v>0.1931</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.383</v>
+        <v>-0.265</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1528</v>
+        <v>0.8262</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2529</v>
+        <v>0.7304</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1001</v>
+        <v>0.0958</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2529</v>
+        <v>0.7304</v>
       </c>
       <c r="I12" t="n">
-        <v>0.205</v>
+        <v>0.3798</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1001</v>
+        <v>0.0958</v>
       </c>
       <c r="K12" t="n">
         <v>51</v>
@@ -989,7 +989,7 @@
         <v>112</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1049</v>
+        <v>0.4756</v>
       </c>
       <c r="N12" t="n">
         <v>163</v>
@@ -998,81 +998,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0646</v>
+        <v>0.4109</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0151</v>
+        <v>0.096</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4182</v>
+        <v>-0.4525</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0646</v>
+        <v>0.4109</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1053</v>
+        <v>0.4135</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.0407</v>
+        <v>-0.0026</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1053</v>
+        <v>0.4135</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8959</v>
+        <v>0.215</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0407</v>
+        <v>-0.0026</v>
       </c>
       <c r="K13" t="n">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="L13" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1447999999999999</v>
+        <v>0.2124</v>
       </c>
       <c r="N13" t="n">
-        <v>251</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.2487</v>
+        <v>0.1245</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0581</v>
+        <v>0.0291</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.543</v>
+        <v>-0.5818</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2487</v>
+        <v>0.1245</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3626</v>
+        <v>0.6377</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1139</v>
+        <v>-0.5132</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3626</v>
+        <v>0.6377</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2939</v>
+        <v>0.3316</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1139</v>
+        <v>-0.5132</v>
       </c>
       <c r="K14" t="n">
         <v>83</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.18</v>
+        <v>-0.1816</v>
       </c>
       <c r="N14" t="n">
         <v>135</v>
@@ -1090,127 +1090,127 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.2833</v>
+        <v>0.1058</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.0247</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5568</v>
+        <v>-0.5903</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2833</v>
+        <v>0.1058</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8011</v>
+        <v>0.8028</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5178</v>
+        <v>-0.697</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8011</v>
+        <v>0.8028</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6493</v>
+        <v>0.4174</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5178</v>
+        <v>-0.697</v>
       </c>
       <c r="K15" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L15" t="n">
         <v>52</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1315</v>
+        <v>-0.2796</v>
       </c>
       <c r="N15" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.4343</v>
+        <v>-0.0308</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1015</v>
+        <v>-0.0072</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6169</v>
+        <v>-0.6519</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4343</v>
+        <v>-0.0308</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5657</v>
+        <v>-0.6512</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>0.6204</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5657</v>
+        <v>-0.6512</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4585</v>
+        <v>-0.3386</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>0.6204</v>
       </c>
       <c r="K16" t="n">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="L16" t="n">
         <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5415</v>
+        <v>0.2817999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>135</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.5158</v>
+        <v>-0.1022</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.1205</v>
+        <v>-0.0239</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6494</v>
+        <v>-0.6842</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5158</v>
+        <v>-0.1022</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2787</v>
+        <v>-0.1839</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7945</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2787</v>
+        <v>-0.1839</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2259</v>
+        <v>-0.0956</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7945</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>83</v>
@@ -1219,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5686</v>
+        <v>-0.01390000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>135</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.2943</v>
+        <v>-1.2843</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.3025</v>
+        <v>-0.3001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9596</v>
+        <v>-1.2178</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2943</v>
+        <v>-1.2843</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5851</v>
+        <v>-0.6022</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2908</v>
+        <v>-0.6821</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5851</v>
+        <v>-0.6022</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2848</v>
+        <v>-0.3131</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2908</v>
+        <v>-0.6821</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="L18" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.994</v>
+        <v>-0.9952000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>159</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.4262</v>
+        <v>-1.3824</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3333</v>
+        <v>-0.3231</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0121</v>
+        <v>-1.2621</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4262</v>
+        <v>-1.3824</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2911</v>
+        <v>-1.3926</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1351</v>
+        <v>0.0102</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2911</v>
+        <v>-1.3926</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0465</v>
+        <v>-0.7241</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1351</v>
+        <v>0.0102</v>
       </c>
       <c r="K19" t="n">
         <v>107</v>
@@ -1311,7 +1311,7 @@
         <v>52</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1816</v>
+        <v>-0.7139</v>
       </c>
       <c r="N19" t="n">
         <v>159</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.6564</v>
+        <v>-1.4133</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.3871</v>
+        <v>-0.3303</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1038</v>
+        <v>-1.276</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6564</v>
+        <v>-1.4133</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6165</v>
+        <v>-1.6471</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0399</v>
+        <v>0.2338</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6165</v>
+        <v>-1.6471</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4997</v>
+        <v>-0.8564000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0399</v>
+        <v>0.2338</v>
       </c>
       <c r="K20" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L20" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5396</v>
+        <v>-0.6226</v>
       </c>
       <c r="N20" t="n">
-        <v>251</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.9022</v>
+        <v>-2.6365</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.6783</v>
+        <v>-0.6162</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6001</v>
+        <v>-1.8283</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9022</v>
+        <v>-2.6365</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4784</v>
+        <v>-1.6871</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4238</v>
+        <v>-0.9494</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4784</v>
+        <v>-1.6871</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1983</v>
+        <v>-0.8772</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4238</v>
+        <v>-0.9494</v>
       </c>
       <c r="K21" t="n">
         <v>139</v>
@@ -1403,7 +1403,7 @@
         <v>112</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6221</v>
+        <v>-1.8266</v>
       </c>
       <c r="N21" t="n">
         <v>251</v>
@@ -1509,10 +1509,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0006</v>
+        <v>0.9809</v>
       </c>
       <c r="J2" t="n">
-        <v>27.0162</v>
+        <v>26.4843</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.23</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6786</v>
+        <v>0.6556</v>
       </c>
       <c r="J3" t="n">
-        <v>18.3222</v>
+        <v>17.7012</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6028</v>
+        <v>0.5813</v>
       </c>
       <c r="J4" t="n">
-        <v>16.2756</v>
+        <v>15.6951</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5271</v>
+        <v>-0.464</v>
       </c>
       <c r="J5" t="n">
-        <v>-14.2317</v>
+        <v>-12.528</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5535</v>
+        <v>-0.4916</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.9445</v>
+        <v>-13.2732</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.45</v>
+        <v>0.5192</v>
       </c>
       <c r="J7" t="n">
-        <v>12.15</v>
+        <v>14.0184</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1225</v>
+        <v>0.1071</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3075</v>
+        <v>2.8917</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1824</v>
+        <v>-0.116</v>
       </c>
       <c r="J9" t="n">
-        <v>-4.9248</v>
+        <v>-3.132</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3508</v>
+        <v>-0.2208</v>
       </c>
       <c r="J10" t="n">
-        <v>-9.4716</v>
+        <v>-5.9616</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5332</v>
+        <v>-0.3472</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.3964</v>
+        <v>-9.3744</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8595</v>
+        <v>0.8353</v>
       </c>
       <c r="J12" t="n">
-        <v>24.066</v>
+        <v>23.3884</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5671</v>
+        <v>0.5387</v>
       </c>
       <c r="J13" t="n">
-        <v>15.8788</v>
+        <v>15.0836</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1856</v>
+        <v>0.2122</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1968</v>
+        <v>5.9416</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2111</v>
+        <v>-0.1506</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.9108</v>
+        <v>-4.2168</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4627</v>
+        <v>-0.4005</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.9556</v>
+        <v>-11.214</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0963</v>
+        <v>0.0785</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6964</v>
+        <v>2.198</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0355</v>
+        <v>0.0104</v>
       </c>
       <c r="J18" t="n">
-        <v>0.994</v>
+        <v>0.2912</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>0.96</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.073</v>
+        <v>-0.0586</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.044</v>
+        <v>-1.6408</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.167</v>
+        <v>-0.1056</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.676</v>
+        <v>-2.9568</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3682</v>
+        <v>-0.2318</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.3096</v>
+        <v>-6.4904</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2194</v>
+        <v>0.2123</v>
       </c>
       <c r="J22" t="n">
-        <v>5.7044</v>
+        <v>5.5198</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>0.87</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1949</v>
+        <v>-0.1504</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.0674</v>
+        <v>-3.9104</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.297</v>
+        <v>-0.1999</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.722</v>
+        <v>-5.1974</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3641</v>
+        <v>-0.239</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.4666</v>
+        <v>-6.214</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5245</v>
+        <v>-0.3446</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.637</v>
+        <v>-8.9596</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9439</v>
       </c>
       <c r="J27" t="n">
-        <v>24.44</v>
+        <v>24.5414</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7068</v>
+        <v>0.7194</v>
       </c>
       <c r="J28" t="n">
-        <v>18.3768</v>
+        <v>18.7044</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.27</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7068</v>
+        <v>0.7194</v>
       </c>
       <c r="J29" t="n">
-        <v>18.3768</v>
+        <v>18.7044</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2833</v>
+        <v>0.3533</v>
       </c>
       <c r="J30" t="n">
-        <v>7.3658</v>
+        <v>9.1858</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>1.07</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1382</v>
+        <v>0.2101</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5932</v>
+        <v>5.4626</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4793</v>
+        <v>0.5669</v>
       </c>
       <c r="J32" t="n">
-        <v>14.379</v>
+        <v>17.007</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.13</v>
       </c>
       <c r="I33" t="n">
-        <v>0.261</v>
+        <v>0.2953</v>
       </c>
       <c r="J33" t="n">
-        <v>7.83</v>
+        <v>8.859</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0616</v>
+        <v>-0.0244</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.848</v>
+        <v>-0.732</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1702</v>
+        <v>-0.0927</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.106</v>
+        <v>-2.781</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2733</v>
+        <v>-0.1611</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.199</v>
+        <v>-4.833</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>1.051</v>
+        <v>1.0243</v>
       </c>
       <c r="J37" t="n">
-        <v>31.53</v>
+        <v>30.729</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9649</v>
+        <v>0.9516</v>
       </c>
       <c r="J38" t="n">
-        <v>28.947</v>
+        <v>28.548</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4461</v>
+        <v>0.4484</v>
       </c>
       <c r="J39" t="n">
-        <v>13.383</v>
+        <v>13.452</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3359</v>
+        <v>-0.265</v>
       </c>
       <c r="J40" t="n">
-        <v>-10.077</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6879</v>
+        <v>-0.6322</v>
       </c>
       <c r="J41" t="n">
-        <v>-20.637</v>
+        <v>-18.966</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3516</v>
+        <v>0.3992</v>
       </c>
       <c r="J42" t="n">
-        <v>10.1964</v>
+        <v>11.5768</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.15</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3061</v>
+        <v>0.3427</v>
       </c>
       <c r="J43" t="n">
-        <v>8.876899999999999</v>
+        <v>9.9383</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.034</v>
+        <v>0.0368</v>
       </c>
       <c r="J44" t="n">
-        <v>0.986</v>
+        <v>1.0672</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0453</v>
+        <v>-0.0211</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.3137</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.3276</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.7494</v>
+        <v>-9.500400000000001</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7548</v>
+        <v>0.7153</v>
       </c>
       <c r="J47" t="n">
-        <v>21.8892</v>
+        <v>20.7437</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5796</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>16.8084</v>
+        <v>15.5092</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2209</v>
+        <v>0.1925</v>
       </c>
       <c r="J49" t="n">
-        <v>6.4061</v>
+        <v>5.5825</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.83</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5984</v>
+        <v>-0.5476</v>
       </c>
       <c r="J50" t="n">
-        <v>-17.3536</v>
+        <v>-15.8804</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6745</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-19.5605</v>
+        <v>-18.1685</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.26</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4172</v>
+        <v>0.3592</v>
       </c>
       <c r="J52" t="n">
-        <v>11.6816</v>
+        <v>10.0576</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>1.17</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2816</v>
+        <v>0.2491</v>
       </c>
       <c r="J53" t="n">
-        <v>7.8848</v>
+        <v>6.9748</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2433</v>
+        <v>0.2242</v>
       </c>
       <c r="J54" t="n">
-        <v>6.8124</v>
+        <v>6.2776</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1867</v>
+        <v>0.1853</v>
       </c>
       <c r="J55" t="n">
-        <v>5.2276</v>
+        <v>5.1884</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0612</v>
+        <v>0.0828</v>
       </c>
       <c r="J56" t="n">
-        <v>1.7136</v>
+        <v>2.3184</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3286</v>
+        <v>0.2771</v>
       </c>
       <c r="J57" t="n">
-        <v>9.200799999999999</v>
+        <v>7.7588</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.128</v>
+        <v>-0.0832</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.584</v>
+        <v>-2.3296</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1703</v>
+        <v>-0.1061</v>
       </c>
       <c r="J59" t="n">
-        <v>-4.7684</v>
+        <v>-2.9708</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.208</v>
+        <v>-0.1284</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.824</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3398</v>
+        <v>-0.2124</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.5144</v>
+        <v>-5.9472</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.04</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1429</v>
+        <v>0.1315</v>
       </c>
       <c r="J62" t="n">
-        <v>3.7154</v>
+        <v>3.419</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0508</v>
       </c>
       <c r="J63" t="n">
-        <v>1.9084</v>
+        <v>1.3208</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1414</v>
+        <v>-0.0939</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.6764</v>
+        <v>-2.4414</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2025</v>
+        <v>-0.1272</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.265</v>
+        <v>-3.3072</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3813</v>
+        <v>-0.2411</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.9138</v>
+        <v>-6.2686</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.47</v>
       </c>
       <c r="I67" t="n">
-        <v>1.2076</v>
+        <v>1.1268</v>
       </c>
       <c r="J67" t="n">
-        <v>31.3976</v>
+        <v>29.2968</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.7008</v>
+        <v>0.6788</v>
       </c>
       <c r="J68" t="n">
-        <v>18.2208</v>
+        <v>17.6488</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.24</v>
       </c>
       <c r="I69" t="n">
-        <v>0.7008</v>
+        <v>0.6788</v>
       </c>
       <c r="J69" t="n">
-        <v>18.2208</v>
+        <v>17.6488</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4927</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.4274</v>
+        <v>-12.8102</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.74</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8462</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="J71" t="n">
-        <v>-22.0012</v>
+        <v>-20.9274</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2066</v>
+        <v>0.1994</v>
       </c>
       <c r="J72" t="n">
-        <v>5.5782</v>
+        <v>5.3838</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0756</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.1654</v>
+        <v>-2.0412</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1966</v>
+        <v>-0.1432</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.3082</v>
+        <v>-3.8664</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3456</v>
+        <v>-0.2234</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.331200000000001</v>
+        <v>-6.0318</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5194</v>
+        <v>-0.3395</v>
       </c>
       <c r="J76" t="n">
-        <v>-14.0238</v>
+        <v>-9.166499999999999</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.67</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5465</v>
+        <v>1.3543</v>
       </c>
       <c r="J77" t="n">
-        <v>41.7555</v>
+        <v>36.5661</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.29</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7658</v>
+        <v>0.7694</v>
       </c>
       <c r="J78" t="n">
-        <v>20.6766</v>
+        <v>20.7738</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.4596</v>
+        <v>0.5117</v>
       </c>
       <c r="J79" t="n">
-        <v>12.4092</v>
+        <v>13.8159</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3298</v>
+        <v>-0.2515</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.9046</v>
+        <v>-6.7905</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3915</v>
+        <v>-0.3149</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.5705</v>
+        <v>-8.5023</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>0.76</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.3181</v>
+        <v>-0.245</v>
       </c>
       <c r="J82" t="n">
-        <v>-7.6344</v>
+        <v>-5.88</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>0.75</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.3353</v>
+        <v>-0.2546</v>
       </c>
       <c r="J83" t="n">
-        <v>-8.0472</v>
+        <v>-6.1104</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3531</v>
+        <v>-0.264</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.474399999999999</v>
+        <v>-6.336</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4167</v>
+        <v>-0.2908</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.0008</v>
+        <v>-6.9792</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.66</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4981</v>
+        <v>-0.337</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.9544</v>
+        <v>-8.087999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.59</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3216</v>
+        <v>1.2185</v>
       </c>
       <c r="J87" t="n">
-        <v>31.7184</v>
+        <v>29.244</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.46</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0585</v>
+        <v>1.06</v>
       </c>
       <c r="J88" t="n">
-        <v>25.404</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5965</v>
+        <v>0.6947</v>
       </c>
       <c r="J89" t="n">
-        <v>14.316</v>
+        <v>16.6728</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>1.26</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5729</v>
+        <v>0.6715</v>
       </c>
       <c r="J90" t="n">
-        <v>13.7496</v>
+        <v>16.116</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I91" t="n">
-        <v>0.5254</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>12.6096</v>
+        <v>14.988</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3375</v>
+        <v>0.3558</v>
       </c>
       <c r="J92" t="n">
-        <v>9.449999999999999</v>
+        <v>9.962400000000001</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2053</v>
+        <v>0.2047</v>
       </c>
       <c r="J93" t="n">
-        <v>5.7484</v>
+        <v>5.7316</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3323</v>
+        <v>-0.2095</v>
       </c>
       <c r="J94" t="n">
-        <v>-9.304399999999999</v>
+        <v>-5.866</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3477</v>
+        <v>-0.2196</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.7356</v>
+        <v>-6.1488</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.76</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4214</v>
+        <v>-0.2691</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.7992</v>
+        <v>-7.5348</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2262</v>
+        <v>0.8697</v>
       </c>
       <c r="J97" t="n">
-        <v>34.3336</v>
+        <v>24.3516</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5391</v>
+        <v>0.4678</v>
       </c>
       <c r="J98" t="n">
-        <v>15.0948</v>
+        <v>13.0984</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3264</v>
+        <v>0.3649</v>
       </c>
       <c r="J99" t="n">
-        <v>9.139200000000001</v>
+        <v>10.2172</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>1.07</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1504</v>
+        <v>0.2168</v>
       </c>
       <c r="J100" t="n">
-        <v>4.2112</v>
+        <v>6.0704</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>1.06</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1191</v>
+        <v>0.1861</v>
       </c>
       <c r="J101" t="n">
-        <v>3.3348</v>
+        <v>5.2108</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4433</v>
+        <v>0.4373</v>
       </c>
       <c r="J102" t="n">
-        <v>12.8557</v>
+        <v>12.6817</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1424</v>
+        <v>-0.1036</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.1296</v>
+        <v>-3.0044</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1682</v>
+        <v>-0.1144</v>
       </c>
       <c r="J104" t="n">
-        <v>-4.8778</v>
+        <v>-3.3176</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2099</v>
+        <v>-0.1358</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.0871</v>
+        <v>-3.9382</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6065</v>
+        <v>-0.4009</v>
       </c>
       <c r="J106" t="n">
-        <v>-17.5885</v>
+        <v>-11.6261</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1492</v>
+        <v>0.82</v>
       </c>
       <c r="J107" t="n">
-        <v>33.3268</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.28</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7538</v>
+        <v>0.58</v>
       </c>
       <c r="J108" t="n">
-        <v>21.8602</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.12</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3025</v>
+        <v>0.35</v>
       </c>
       <c r="J109" t="n">
-        <v>8.772500000000001</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.1563</v>
       </c>
       <c r="J110" t="n">
-        <v>2.6216</v>
+        <v>4.5327</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>1.01</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0586</v>
+        <v>0.0103</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.6994</v>
+        <v>0.2987</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5796</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J112" t="n">
-        <v>16.8084</v>
+        <v>15.8601</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0261</v>
+        <v>-0.0312</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.7569</v>
+        <v>-0.9048</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.05</v>
+        <v>-0.0454</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.45</v>
+        <v>-1.3166</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.258</v>
+        <v>-0.16</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.482</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>0.55</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6974</v>
+        <v>-0.4684</v>
       </c>
       <c r="J116" t="n">
-        <v>-20.2246</v>
+        <v>-13.5836</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2024</v>
+        <v>0.8501</v>
       </c>
       <c r="J117" t="n">
-        <v>34.8696</v>
+        <v>24.6529</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4854</v>
+        <v>0.4179</v>
       </c>
       <c r="J118" t="n">
-        <v>14.0766</v>
+        <v>12.1191</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2219</v>
+        <v>0.2634</v>
       </c>
       <c r="J119" t="n">
-        <v>6.4351</v>
+        <v>7.6386</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.23</v>
+        <v>-0.1613</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.67</v>
+        <v>-4.6777</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.92</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3922</v>
+        <v>-0.3236</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.3738</v>
+        <v>-9.384399999999999</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.14</v>
+        <v>0.1129</v>
       </c>
       <c r="J122" t="n">
-        <v>3.22</v>
+        <v>2.5967</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0805</v>
+        <v>0.0428</v>
       </c>
       <c r="J123" t="n">
-        <v>1.8515</v>
+        <v>0.9844000000000001</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3452</v>
+        <v>-0.2286</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.9396</v>
+        <v>-5.2578</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4811</v>
+        <v>-0.3153</v>
       </c>
       <c r="J125" t="n">
-        <v>-11.0653</v>
+        <v>-7.2519</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5365</v>
+        <v>-0.3532</v>
       </c>
       <c r="J126" t="n">
-        <v>-12.3395</v>
+        <v>-8.1236</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2959</v>
+        <v>0.9186</v>
       </c>
       <c r="J127" t="n">
-        <v>29.8057</v>
+        <v>21.1278</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.27</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.5574</v>
       </c>
       <c r="J128" t="n">
-        <v>15.709</v>
+        <v>12.8202</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.25</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6199</v>
+        <v>0.5312</v>
       </c>
       <c r="J129" t="n">
-        <v>14.2577</v>
+        <v>12.2176</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.2959</v>
+        <v>0.357</v>
       </c>
       <c r="J130" t="n">
-        <v>6.8057</v>
+        <v>8.211</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0949</v>
+        <v>0.1715</v>
       </c>
       <c r="J131" t="n">
-        <v>2.1827</v>
+        <v>3.9445</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4889/event_4889_evp_summary.xlsx
+++ b/database/event/4889/event_4889_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.1577</v>
+        <v>4.0788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9717</v>
+        <v>0.9532</v>
       </c>
       <c r="D2" t="n">
-        <v>1.239</v>
+        <v>1.2326</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1577</v>
+        <v>4.0788</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5016</v>
+        <v>2.4347</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6561</v>
+        <v>1.6441</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3276</v>
+        <v>3.1388</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7302</v>
+        <v>1.6949</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6561</v>
+        <v>1.6441</v>
       </c>
       <c r="K2" t="n">
         <v>51</v>
@@ -529,7 +529,7 @@
         <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3863</v>
+        <v>3.339</v>
       </c>
       <c r="N2" t="n">
         <v>163</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.0749</v>
+        <v>4.0781</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9523</v>
+        <v>0.9530999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2016</v>
+        <v>1.2322</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0749</v>
+        <v>4.0781</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5549</v>
+        <v>1.4467</v>
       </c>
       <c r="G3" t="n">
-        <v>2.52</v>
+        <v>2.6314</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5549</v>
+        <v>1.4467</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8085</v>
+        <v>0.7812</v>
       </c>
       <c r="J3" t="n">
-        <v>2.52</v>
+        <v>2.6314</v>
       </c>
       <c r="K3" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>112</v>
       </c>
       <c r="M3" t="n">
-        <v>3.3285</v>
+        <v>3.4126</v>
       </c>
       <c r="N3" t="n">
         <v>163</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0605</v>
+        <v>3.9867</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9489</v>
+        <v>0.9317</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1951</v>
+        <v>1.1906</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0605</v>
+        <v>3.9867</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0049</v>
+        <v>2.9172</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0556</v>
+        <v>1.0695</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1012</v>
+        <v>4.7306</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6524</v>
+        <v>2.5545</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0556</v>
+        <v>1.0695</v>
       </c>
       <c r="K4" t="n">
         <v>139</v>
@@ -621,7 +621,7 @@
         <v>112</v>
       </c>
       <c r="M4" t="n">
-        <v>3.708</v>
+        <v>3.624</v>
       </c>
       <c r="N4" t="n">
         <v>251</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7615</v>
+        <v>3.6874</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8791</v>
+        <v>0.8618</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0601</v>
+        <v>1.0544</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7615</v>
+        <v>3.6874</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3345</v>
+        <v>2.5725</v>
       </c>
       <c r="G5" t="n">
-        <v>0.427</v>
+        <v>1.1149</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2625</v>
+        <v>3.5934</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2562</v>
+        <v>1.9404</v>
       </c>
       <c r="J5" t="n">
-        <v>0.427</v>
+        <v>1.1149</v>
       </c>
       <c r="K5" t="n">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="L5" t="n">
         <v>112</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6832</v>
+        <v>3.0553</v>
       </c>
       <c r="N5" t="n">
-        <v>251</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6892</v>
+        <v>3.6266</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8622</v>
+        <v>0.8475</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0275</v>
+        <v>1.0267</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6892</v>
+        <v>3.6266</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6373</v>
+        <v>3.197</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0519</v>
+        <v>0.4296</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8057</v>
+        <v>5.654</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9788</v>
+        <v>3.0531</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0519</v>
+        <v>0.4296</v>
       </c>
       <c r="K6" t="n">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="L6" t="n">
         <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>3.0307</v>
+        <v>3.4827</v>
       </c>
       <c r="N6" t="n">
-        <v>163</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.339</v>
+        <v>3.2914</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7803</v>
+        <v>0.7692</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8694</v>
+        <v>0.8741</v>
       </c>
       <c r="E7" t="n">
-        <v>3.339</v>
+        <v>3.2914</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3436</v>
+        <v>2.2597</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9954</v>
+        <v>1.0317</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7712</v>
+        <v>2.5613</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4409</v>
+        <v>1.3831</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9954</v>
+        <v>1.0317</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -759,7 +759,7 @@
         <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4363</v>
+        <v>2.4148</v>
       </c>
       <c r="N7" t="n">
         <v>163</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.3051</v>
+        <v>1.2952</v>
       </c>
       <c r="C8" t="n">
-        <v>0.305</v>
+        <v>0.3027</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0488</v>
+        <v>-0.0346</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3051</v>
+        <v>1.2952</v>
       </c>
       <c r="F8" t="n">
-        <v>0.356</v>
+        <v>0.2459</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9491000000000001</v>
+        <v>1.0493</v>
       </c>
       <c r="H8" t="n">
-        <v>0.356</v>
+        <v>0.2459</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1851</v>
+        <v>0.1328</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9491000000000001</v>
+        <v>1.0493</v>
       </c>
       <c r="K8" t="n">
         <v>107</v>
@@ -805,7 +805,7 @@
         <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1342</v>
+        <v>1.1821</v>
       </c>
       <c r="N8" t="n">
         <v>159</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.1699</v>
+        <v>1.1568</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2734</v>
+        <v>0.2703</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1099</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1699</v>
+        <v>1.1568</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8409</v>
+        <v>-0.7909</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.671</v>
+        <v>1.9478</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8409</v>
+        <v>-0.7909</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9572000000000001</v>
+        <v>-0.4271</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.671</v>
+        <v>1.9478</v>
       </c>
       <c r="K9" t="n">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L9" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2862</v>
+        <v>1.5207</v>
       </c>
       <c r="N9" t="n">
-        <v>251</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.0431</v>
+        <v>1.0358</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2438</v>
+        <v>0.2421</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1671</v>
+        <v>-0.1527</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0431</v>
+        <v>1.0358</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7256</v>
+        <v>1.7652</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7687</v>
+        <v>-0.7294</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7256</v>
+        <v>1.7652</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3773</v>
+        <v>0.9532</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7687</v>
+        <v>-0.7294</v>
       </c>
       <c r="K10" t="n">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3914</v>
+        <v>0.2238</v>
       </c>
       <c r="N10" t="n">
-        <v>159</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9669</v>
+        <v>0.9821</v>
       </c>
       <c r="C11" t="n">
-        <v>0.226</v>
+        <v>0.2295</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2015</v>
+        <v>-0.1771</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9669</v>
+        <v>0.9821</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7353</v>
+        <v>0.7083</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2316</v>
+        <v>0.2738</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7353</v>
+        <v>0.7083</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3823</v>
+        <v>0.3825</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2316</v>
+        <v>0.2738</v>
       </c>
       <c r="K11" t="n">
         <v>83</v>
@@ -943,7 +943,7 @@
         <v>52</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6139</v>
+        <v>0.6563</v>
       </c>
       <c r="N11" t="n">
         <v>135</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8262</v>
+        <v>0.862</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1931</v>
+        <v>0.2015</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.265</v>
+        <v>-0.2318</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8262</v>
+        <v>0.862</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7304</v>
+        <v>0.6924</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0958</v>
+        <v>0.1696</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7304</v>
+        <v>0.6924</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3798</v>
+        <v>0.3739</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0958</v>
+        <v>0.1696</v>
       </c>
       <c r="K12" t="n">
         <v>51</v>
@@ -989,7 +989,7 @@
         <v>112</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4756</v>
+        <v>0.5435</v>
       </c>
       <c r="N12" t="n">
         <v>163</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4109</v>
+        <v>0.4008</v>
       </c>
       <c r="C13" t="n">
-        <v>0.096</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4525</v>
+        <v>-0.4418</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4109</v>
+        <v>0.4008</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4135</v>
+        <v>0.4245</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0026</v>
+        <v>-0.0237</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4135</v>
+        <v>0.4245</v>
       </c>
       <c r="I13" t="n">
-        <v>0.215</v>
+        <v>0.2292</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0026</v>
+        <v>-0.0237</v>
       </c>
       <c r="K13" t="n">
         <v>83</v>
@@ -1035,7 +1035,7 @@
         <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2124</v>
+        <v>0.2055</v>
       </c>
       <c r="N13" t="n">
         <v>135</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.1245</v>
+        <v>0.101</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0291</v>
+        <v>0.0236</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5818</v>
+        <v>-0.5782</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1245</v>
+        <v>0.101</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6377</v>
+        <v>0.823</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.5132</v>
+        <v>-0.722</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6377</v>
+        <v>0.823</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3316</v>
+        <v>0.4444</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5132</v>
+        <v>-0.722</v>
       </c>
       <c r="K14" t="n">
         <v>83</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1816</v>
+        <v>-0.2776</v>
       </c>
       <c r="N14" t="n">
         <v>135</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1058</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0247</v>
+        <v>0.0183</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5903</v>
+        <v>-0.5886</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1058</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8028</v>
+        <v>0.6211</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.697</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8028</v>
+        <v>0.6211</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4174</v>
+        <v>0.3354</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.697</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>83</v>
@@ -1127,7 +1127,7 @@
         <v>52</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2796</v>
+        <v>-0.2074</v>
       </c>
       <c r="N15" t="n">
         <v>135</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0308</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0072</v>
+        <v>-0.0158</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6519</v>
+        <v>-0.655</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0308</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6512</v>
+        <v>-0.7148</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6204</v>
+        <v>0.6472</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6512</v>
+        <v>-0.7148</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3386</v>
+        <v>-0.386</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6204</v>
+        <v>0.6472</v>
       </c>
       <c r="K16" t="n">
         <v>107</v>
@@ -1173,7 +1173,7 @@
         <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2817999999999999</v>
+        <v>0.2612</v>
       </c>
       <c r="N16" t="n">
         <v>159</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.1022</v>
+        <v>-0.1306</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0239</v>
+        <v>-0.0305</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6842</v>
+        <v>-0.6837</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1022</v>
+        <v>-0.1306</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1839</v>
+        <v>-0.1989</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0683</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1839</v>
+        <v>-0.1989</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0956</v>
+        <v>-0.1074</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.0683</v>
       </c>
       <c r="K17" t="n">
         <v>83</v>
@@ -1219,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.01390000000000001</v>
+        <v>-0.0391</v>
       </c>
       <c r="N17" t="n">
         <v>135</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.2843</v>
+        <v>-1.242</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.3001</v>
+        <v>-0.2903</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2178</v>
+        <v>-1.1896</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2843</v>
+        <v>-1.242</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6022</v>
+        <v>-0.5137</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6821</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6022</v>
+        <v>-0.5137</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3131</v>
+        <v>-0.2774</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6821</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>139</v>
@@ -1265,7 +1265,7 @@
         <v>112</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9952000000000001</v>
+        <v>-1.0057</v>
       </c>
       <c r="N18" t="n">
         <v>251</v>
@@ -1274,35 +1274,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.3824</v>
+        <v>-1.3793</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3231</v>
+        <v>-0.3223</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2621</v>
+        <v>-1.2521</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3824</v>
+        <v>-1.3793</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3926</v>
+        <v>-1.6887</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0102</v>
+        <v>0.3094</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3926</v>
+        <v>-1.6887</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7241</v>
+        <v>-0.9119</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0102</v>
+        <v>0.3094</v>
       </c>
       <c r="K19" t="n">
         <v>107</v>
@@ -1311,7 +1311,7 @@
         <v>52</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7139</v>
+        <v>-0.6025</v>
       </c>
       <c r="N19" t="n">
         <v>159</v>
@@ -1320,35 +1320,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.4133</v>
+        <v>-1.4204</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.3303</v>
+        <v>-0.332</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.276</v>
+        <v>-1.2708</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4133</v>
+        <v>-1.4204</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6471</v>
+        <v>-1.4543</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2338</v>
+        <v>0.0339</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6471</v>
+        <v>-1.4543</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8564000000000001</v>
+        <v>-0.7853</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2338</v>
+        <v>0.0339</v>
       </c>
       <c r="K20" t="n">
         <v>107</v>
@@ -1357,7 +1357,7 @@
         <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6226</v>
+        <v>-0.7514</v>
       </c>
       <c r="N20" t="n">
         <v>159</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.6365</v>
+        <v>-2.5781</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.6162</v>
+        <v>-0.6025</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8283</v>
+        <v>-1.7978</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6365</v>
+        <v>-2.5781</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6871</v>
+        <v>-1.5772</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9494</v>
+        <v>-1.0009</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6871</v>
+        <v>-1.5772</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8772</v>
+        <v>-0.8517</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9494</v>
+        <v>-1.0009</v>
       </c>
       <c r="K21" t="n">
         <v>139</v>
@@ -1403,7 +1403,7 @@
         <v>112</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8266</v>
+        <v>-1.8526</v>
       </c>
       <c r="N21" t="n">
         <v>251</v>
@@ -1509,10 +1509,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9809</v>
+        <v>0.9174</v>
       </c>
       <c r="J2" t="n">
-        <v>26.4843</v>
+        <v>24.7698</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.23</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6556</v>
+        <v>0.6259</v>
       </c>
       <c r="J3" t="n">
-        <v>17.7012</v>
+        <v>16.8993</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5813</v>
+        <v>0.5596</v>
       </c>
       <c r="J4" t="n">
-        <v>15.6951</v>
+        <v>15.1092</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.464</v>
+        <v>-0.4405</v>
       </c>
       <c r="J5" t="n">
-        <v>-12.528</v>
+        <v>-11.8935</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4916</v>
+        <v>-0.4655</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.2732</v>
+        <v>-12.5685</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5192</v>
+        <v>0.5032</v>
       </c>
       <c r="J7" t="n">
-        <v>14.0184</v>
+        <v>13.5864</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1071</v>
+        <v>0.111</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8917</v>
+        <v>2.997</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.116</v>
+        <v>-0.13</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.132</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2208</v>
+        <v>-0.2361</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.9616</v>
+        <v>-6.3747</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3472</v>
+        <v>-0.3597</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.3744</v>
+        <v>-9.7119</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8353</v>
+        <v>0.7821</v>
       </c>
       <c r="J12" t="n">
-        <v>23.3884</v>
+        <v>21.8988</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5387</v>
+        <v>0.5199</v>
       </c>
       <c r="J13" t="n">
-        <v>15.0836</v>
+        <v>14.5572</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2122</v>
+        <v>0.219</v>
       </c>
       <c r="J14" t="n">
-        <v>5.9416</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1506</v>
+        <v>-0.1496</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.2168</v>
+        <v>-4.1888</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4005</v>
+        <v>-0.3842</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.214</v>
+        <v>-10.7576</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0785</v>
+        <v>0.0823</v>
       </c>
       <c r="J17" t="n">
-        <v>2.198</v>
+        <v>2.3044</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0104</v>
+        <v>0.0074</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2912</v>
+        <v>0.2072</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>0.96</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0586</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.6408</v>
+        <v>-1.932</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1056</v>
+        <v>-0.119</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9568</v>
+        <v>-3.332</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2318</v>
+        <v>-0.2468</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.4904</v>
+        <v>-6.9104</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2123</v>
+        <v>0.207</v>
       </c>
       <c r="J22" t="n">
-        <v>5.5198</v>
+        <v>5.382</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>0.87</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1504</v>
+        <v>-0.1675</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.9104</v>
+        <v>-4.355</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1999</v>
+        <v>-0.2178</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.1974</v>
+        <v>-5.6628</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.239</v>
+        <v>-0.2566</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.214</v>
+        <v>-6.6716</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3446</v>
+        <v>-0.3594</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.9596</v>
+        <v>-9.3444</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9439</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>24.5414</v>
+        <v>23.0776</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7194</v>
+        <v>0.6886</v>
       </c>
       <c r="J28" t="n">
-        <v>18.7044</v>
+        <v>17.9036</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.27</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7194</v>
+        <v>0.6886</v>
       </c>
       <c r="J29" t="n">
-        <v>18.7044</v>
+        <v>17.9036</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3533</v>
+        <v>0.358</v>
       </c>
       <c r="J30" t="n">
-        <v>9.1858</v>
+        <v>9.308</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>1.07</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2101</v>
+        <v>0.2253</v>
       </c>
       <c r="J31" t="n">
-        <v>5.4626</v>
+        <v>5.8578</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5669</v>
+        <v>0.5544</v>
       </c>
       <c r="J32" t="n">
-        <v>17.007</v>
+        <v>16.632</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.13</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2953</v>
+        <v>0.3017</v>
       </c>
       <c r="J33" t="n">
-        <v>8.859</v>
+        <v>9.051</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0244</v>
+        <v>-0.0281</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.732</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0927</v>
+        <v>-0.1026</v>
       </c>
       <c r="J35" t="n">
-        <v>-2.781</v>
+        <v>-3.078</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1611</v>
+        <v>-0.1731</v>
       </c>
       <c r="J36" t="n">
-        <v>-4.833</v>
+        <v>-5.193</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0243</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>30.729</v>
+        <v>28.986</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9516</v>
+        <v>0.8897</v>
       </c>
       <c r="J38" t="n">
-        <v>28.548</v>
+        <v>26.691</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4484</v>
+        <v>0.4412</v>
       </c>
       <c r="J39" t="n">
-        <v>13.452</v>
+        <v>13.236</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.265</v>
+        <v>-0.2554</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.95</v>
+        <v>-7.662</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6322</v>
+        <v>-0.5903</v>
       </c>
       <c r="J41" t="n">
-        <v>-18.966</v>
+        <v>-17.709</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3992</v>
+        <v>0.3975</v>
       </c>
       <c r="J42" t="n">
-        <v>11.5768</v>
+        <v>11.5275</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.15</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3427</v>
+        <v>0.3445</v>
       </c>
       <c r="J43" t="n">
-        <v>9.9383</v>
+        <v>9.990500000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0368</v>
+        <v>0.0427</v>
       </c>
       <c r="J44" t="n">
-        <v>1.0672</v>
+        <v>1.2383</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0211</v>
+        <v>-0.0257</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.6119</v>
+        <v>-0.7453</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3276</v>
+        <v>-0.3392</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.500400000000001</v>
+        <v>-9.8368</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7153</v>
+        <v>0.6721</v>
       </c>
       <c r="J47" t="n">
-        <v>20.7437</v>
+        <v>19.4909</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5119</v>
       </c>
       <c r="J48" t="n">
-        <v>15.5092</v>
+        <v>14.8451</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1925</v>
+        <v>0.197</v>
       </c>
       <c r="J49" t="n">
-        <v>5.5825</v>
+        <v>5.713</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.83</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5476</v>
+        <v>-0.5209</v>
       </c>
       <c r="J50" t="n">
-        <v>-15.8804</v>
+        <v>-15.1061</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-18.1685</v>
+        <v>-17.1448</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.26</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3592</v>
+        <v>0.3733</v>
       </c>
       <c r="J52" t="n">
-        <v>10.0576</v>
+        <v>10.4524</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>1.17</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2491</v>
+        <v>0.2659</v>
       </c>
       <c r="J53" t="n">
-        <v>6.9748</v>
+        <v>7.4452</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2242</v>
+        <v>0.2411</v>
       </c>
       <c r="J54" t="n">
-        <v>6.2776</v>
+        <v>6.7508</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1853</v>
+        <v>0.2022</v>
       </c>
       <c r="J55" t="n">
-        <v>5.1884</v>
+        <v>5.6616</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0828</v>
+        <v>0.0977</v>
       </c>
       <c r="J56" t="n">
-        <v>2.3184</v>
+        <v>2.7356</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2771</v>
+        <v>0.281</v>
       </c>
       <c r="J57" t="n">
-        <v>7.7588</v>
+        <v>7.868</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0832</v>
+        <v>-0.0953</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.3296</v>
+        <v>-2.6684</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1061</v>
+        <v>-0.1194</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.9708</v>
+        <v>-3.3432</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1284</v>
+        <v>-0.1424</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.5952</v>
+        <v>-3.9872</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2124</v>
+        <v>-0.2274</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.9472</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.04</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1315</v>
+        <v>0.1358</v>
       </c>
       <c r="J62" t="n">
-        <v>3.419</v>
+        <v>3.5308</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0508</v>
+        <v>0.0527</v>
       </c>
       <c r="J63" t="n">
-        <v>1.3208</v>
+        <v>1.3702</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0939</v>
+        <v>-0.1068</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.4414</v>
+        <v>-2.7768</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1272</v>
+        <v>-0.1415</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.3072</v>
+        <v>-3.679</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2411</v>
+        <v>-0.2561</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.2686</v>
+        <v>-6.6586</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.47</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1268</v>
+        <v>1.0838</v>
       </c>
       <c r="J67" t="n">
-        <v>29.2968</v>
+        <v>28.1788</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6788</v>
+        <v>0.6466</v>
       </c>
       <c r="J68" t="n">
-        <v>17.6488</v>
+        <v>16.8116</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.24</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6788</v>
+        <v>0.6466</v>
       </c>
       <c r="J69" t="n">
-        <v>17.6488</v>
+        <v>16.8116</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4927</v>
+        <v>-0.4663</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.8102</v>
+        <v>-12.1238</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.74</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.7439</v>
       </c>
       <c r="J71" t="n">
-        <v>-20.9274</v>
+        <v>-19.3414</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1994</v>
+        <v>0.1975</v>
       </c>
       <c r="J72" t="n">
-        <v>5.3838</v>
+        <v>5.3325</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0756</v>
+        <v>-0.0895</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.0412</v>
+        <v>-2.4165</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1432</v>
+        <v>-0.1594</v>
       </c>
       <c r="J74" t="n">
-        <v>-3.8664</v>
+        <v>-4.3038</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2234</v>
+        <v>-0.2403</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.0318</v>
+        <v>-6.4881</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3395</v>
+        <v>-0.3537</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.166499999999999</v>
+        <v>-9.549899999999999</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.67</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3543</v>
+        <v>1.331</v>
       </c>
       <c r="J77" t="n">
-        <v>36.5661</v>
+        <v>35.937</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.29</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7694</v>
+        <v>0.7319</v>
       </c>
       <c r="J78" t="n">
-        <v>20.7738</v>
+        <v>19.7613</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5117</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="J79" t="n">
-        <v>13.8159</v>
+        <v>13.5405</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2515</v>
+        <v>-0.238</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.7905</v>
+        <v>-6.426</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3149</v>
+        <v>-0.2978</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.5023</v>
+        <v>-8.0406</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>0.76</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.245</v>
+        <v>-0.2654</v>
       </c>
       <c r="J82" t="n">
-        <v>-5.88</v>
+        <v>-6.3696</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>0.75</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2546</v>
+        <v>-0.2749</v>
       </c>
       <c r="J83" t="n">
-        <v>-6.1104</v>
+        <v>-6.5976</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.264</v>
+        <v>-0.2841</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.336</v>
+        <v>-6.8184</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2908</v>
+        <v>-0.3105</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.9792</v>
+        <v>-7.452</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.66</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.337</v>
+        <v>-0.3552</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.087999999999999</v>
+        <v>-8.524800000000001</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.59</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2185</v>
+        <v>1.1934</v>
       </c>
       <c r="J87" t="n">
-        <v>29.244</v>
+        <v>28.6416</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.46</v>
       </c>
       <c r="I88" t="n">
-        <v>1.06</v>
+        <v>1.0192</v>
       </c>
       <c r="J88" t="n">
-        <v>25.44</v>
+        <v>24.4608</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6947</v>
+        <v>0.6717</v>
       </c>
       <c r="J89" t="n">
-        <v>16.6728</v>
+        <v>16.1208</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>1.26</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6715</v>
+        <v>0.6512</v>
       </c>
       <c r="J90" t="n">
-        <v>16.116</v>
+        <v>15.6288</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I91" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>14.988</v>
+        <v>14.6256</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3558</v>
+        <v>0.3651</v>
       </c>
       <c r="J92" t="n">
-        <v>9.962400000000001</v>
+        <v>10.2228</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2047</v>
+        <v>0.2069</v>
       </c>
       <c r="J93" t="n">
-        <v>5.7316</v>
+        <v>5.7932</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2095</v>
+        <v>-0.2251</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.866</v>
+        <v>-6.3028</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2196</v>
+        <v>-0.2351</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.1488</v>
+        <v>-6.5828</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.76</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2691</v>
+        <v>-0.284</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.5348</v>
+        <v>-7.952</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.8697</v>
+        <v>0.9587</v>
       </c>
       <c r="J97" t="n">
-        <v>24.3516</v>
+        <v>26.8436</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4678</v>
+        <v>0.5179</v>
       </c>
       <c r="J98" t="n">
-        <v>13.0984</v>
+        <v>14.5012</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3649</v>
+        <v>0.387</v>
       </c>
       <c r="J99" t="n">
-        <v>10.2172</v>
+        <v>10.836</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>1.07</v>
       </c>
       <c r="I100" t="n">
-        <v>0.2168</v>
+        <v>0.23</v>
       </c>
       <c r="J100" t="n">
-        <v>6.0704</v>
+        <v>6.44</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>1.06</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1861</v>
+        <v>0.201</v>
       </c>
       <c r="J101" t="n">
-        <v>5.2108</v>
+        <v>5.628</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4373</v>
+        <v>0.4784</v>
       </c>
       <c r="J102" t="n">
-        <v>12.6817</v>
+        <v>13.8736</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1036</v>
+        <v>-0.1175</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.0044</v>
+        <v>-3.4075</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1144</v>
+        <v>-0.1288</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.3176</v>
+        <v>-3.7352</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1358</v>
+        <v>-0.1509</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.9382</v>
+        <v>-4.3761</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4009</v>
+        <v>-0.4118</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.6261</v>
+        <v>-11.9422</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>0.82</v>
+        <v>0.9049</v>
       </c>
       <c r="J107" t="n">
-        <v>23.78</v>
+        <v>26.2421</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.28</v>
       </c>
       <c r="I108" t="n">
-        <v>0.58</v>
+        <v>0.6432</v>
       </c>
       <c r="J108" t="n">
-        <v>16.82</v>
+        <v>18.6528</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.12</v>
       </c>
       <c r="I109" t="n">
-        <v>0.35</v>
+        <v>0.3636</v>
       </c>
       <c r="J109" t="n">
-        <v>10.15</v>
+        <v>10.5444</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1563</v>
+        <v>0.1722</v>
       </c>
       <c r="J110" t="n">
-        <v>4.5327</v>
+        <v>4.9938</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>1.01</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0103</v>
+        <v>0.0291</v>
       </c>
       <c r="J111" t="n">
-        <v>0.2987</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.6051</v>
       </c>
       <c r="J112" t="n">
-        <v>15.8601</v>
+        <v>17.5479</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0312</v>
+        <v>-0.0391</v>
       </c>
       <c r="J113" t="n">
-        <v>-0.9048</v>
+        <v>-1.1339</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0454</v>
+        <v>-0.0547</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.3166</v>
+        <v>-1.5863</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.16</v>
+        <v>-0.1749</v>
       </c>
       <c r="J115" t="n">
-        <v>-4.64</v>
+        <v>-5.0721</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>0.55</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4684</v>
+        <v>-0.4756</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.5836</v>
+        <v>-13.7924</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8501</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="J117" t="n">
-        <v>24.6529</v>
+        <v>27.086</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4179</v>
+        <v>0.4585</v>
       </c>
       <c r="J118" t="n">
-        <v>12.1191</v>
+        <v>13.2965</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2634</v>
+        <v>0.2695</v>
       </c>
       <c r="J119" t="n">
-        <v>7.6386</v>
+        <v>7.8155</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1613</v>
+        <v>-0.157</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.6777</v>
+        <v>-4.553</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.92</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3236</v>
+        <v>-0.3109</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.384399999999999</v>
+        <v>-9.0161</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1129</v>
+        <v>0.1074</v>
       </c>
       <c r="J122" t="n">
-        <v>2.5967</v>
+        <v>2.4702</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.0428</v>
+        <v>0.031</v>
       </c>
       <c r="J123" t="n">
-        <v>0.9844000000000001</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2286</v>
+        <v>-0.2464</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.2578</v>
+        <v>-5.6672</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3153</v>
+        <v>-0.3313</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.2519</v>
+        <v>-7.6199</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3532</v>
+        <v>-0.3679</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.1236</v>
+        <v>-8.4617</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>0.9186</v>
+        <v>1.0138</v>
       </c>
       <c r="J127" t="n">
-        <v>21.1278</v>
+        <v>23.3174</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.27</v>
       </c>
       <c r="I128" t="n">
-        <v>0.5574</v>
+        <v>0.6203</v>
       </c>
       <c r="J128" t="n">
-        <v>12.8202</v>
+        <v>14.2669</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.25</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5312</v>
+        <v>0.5908</v>
       </c>
       <c r="J129" t="n">
-        <v>12.2176</v>
+        <v>13.5884</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.357</v>
+        <v>0.3777</v>
       </c>
       <c r="J130" t="n">
-        <v>8.211</v>
+        <v>8.687099999999999</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1715</v>
+        <v>0.1909</v>
       </c>
       <c r="J131" t="n">
-        <v>3.9445</v>
+        <v>4.3907</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4889/event_4889_evp_summary.xlsx
+++ b/database/event/4889/event_4889_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.0788</v>
+        <v>4.0815</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9532</v>
+        <v>0.9539</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2326</v>
+        <v>1.2535</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0788</v>
+        <v>4.0815</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4347</v>
+        <v>1.4647</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6441</v>
+        <v>2.6168</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1388</v>
+        <v>1.4647</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6949</v>
+        <v>0.8224</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6441</v>
+        <v>2.6168</v>
       </c>
       <c r="K2" t="n">
         <v>51</v>
@@ -529,7 +529,7 @@
         <v>112</v>
       </c>
       <c r="M2" t="n">
-        <v>3.339</v>
+        <v>3.4392</v>
       </c>
       <c r="N2" t="n">
         <v>163</v>
@@ -538,35 +538,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.0781</v>
+        <v>4.014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9381</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2322</v>
+        <v>1.2228</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0781</v>
+        <v>4.014</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4467</v>
+        <v>2.5111</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6314</v>
+        <v>1.5029</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4467</v>
+        <v>2.9852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7812</v>
+        <v>1.6761</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6314</v>
+        <v>1.5029</v>
       </c>
       <c r="K3" t="n">
         <v>51</v>
@@ -575,7 +575,7 @@
         <v>112</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4126</v>
+        <v>3.179</v>
       </c>
       <c r="N3" t="n">
         <v>163</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9867</v>
+        <v>3.8069</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9317</v>
+        <v>0.8897</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1906</v>
+        <v>1.1284</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9867</v>
+        <v>3.8069</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9172</v>
+        <v>2.8619</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0695</v>
+        <v>0.945</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7306</v>
+        <v>4.3023</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5545</v>
+        <v>2.4156</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0695</v>
+        <v>0.945</v>
       </c>
       <c r="K4" t="n">
         <v>139</v>
@@ -621,7 +621,7 @@
         <v>112</v>
       </c>
       <c r="M4" t="n">
-        <v>3.624</v>
+        <v>3.3606</v>
       </c>
       <c r="N4" t="n">
         <v>251</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6874</v>
+        <v>3.714</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8618</v>
+        <v>0.868</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0544</v>
+        <v>1.0861</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6874</v>
+        <v>3.714</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5725</v>
+        <v>2.6349</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1149</v>
+        <v>1.0791</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5934</v>
+        <v>3.4501</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9404</v>
+        <v>1.9371</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1149</v>
+        <v>1.0791</v>
       </c>
       <c r="K5" t="n">
         <v>51</v>
@@ -667,7 +667,7 @@
         <v>112</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0553</v>
+        <v>3.0162</v>
       </c>
       <c r="N5" t="n">
         <v>163</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6266</v>
+        <v>3.4665</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8475</v>
+        <v>0.8101</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0267</v>
+        <v>0.9734</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6266</v>
+        <v>3.4665</v>
       </c>
       <c r="F6" t="n">
-        <v>3.197</v>
+        <v>3.1264</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4296</v>
+        <v>0.3401</v>
       </c>
       <c r="H6" t="n">
-        <v>5.654</v>
+        <v>5.2952</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0531</v>
+        <v>2.9731</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4296</v>
+        <v>0.3401</v>
       </c>
       <c r="K6" t="n">
         <v>139</v>
@@ -713,7 +713,7 @@
         <v>112</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4827</v>
+        <v>3.3132</v>
       </c>
       <c r="N6" t="n">
         <v>251</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2914</v>
+        <v>3.3573</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7692</v>
+        <v>0.7846</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8741</v>
+        <v>0.9236</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2914</v>
+        <v>3.3573</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2597</v>
+        <v>2.3475</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0317</v>
+        <v>1.0098</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5613</v>
+        <v>2.3707</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3831</v>
+        <v>1.3311</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0317</v>
+        <v>1.0098</v>
       </c>
       <c r="K7" t="n">
         <v>51</v>
@@ -759,7 +759,7 @@
         <v>112</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4148</v>
+        <v>2.3409</v>
       </c>
       <c r="N7" t="n">
         <v>163</v>
@@ -768,35 +768,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2952</v>
+        <v>1.1804</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3027</v>
+        <v>0.2759</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0346</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2952</v>
+        <v>1.1804</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2459</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0493</v>
+        <v>1.9218</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2459</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1328</v>
+        <v>-0.4163</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0493</v>
+        <v>1.9218</v>
       </c>
       <c r="K8" t="n">
         <v>107</v>
@@ -805,7 +805,7 @@
         <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1821</v>
+        <v>1.5055</v>
       </c>
       <c r="N8" t="n">
         <v>159</v>
@@ -814,35 +814,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.1568</v>
+        <v>1.1229</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2703</v>
+        <v>0.2624</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1568</v>
+        <v>1.1229</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7909</v>
+        <v>0.1124</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9478</v>
+        <v>1.0105</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7909</v>
+        <v>0.1124</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4271</v>
+        <v>0.0631</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9478</v>
+        <v>1.0105</v>
       </c>
       <c r="K9" t="n">
         <v>107</v>
@@ -851,7 +851,7 @@
         <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5207</v>
+        <v>1.0736</v>
       </c>
       <c r="N9" t="n">
         <v>159</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.0358</v>
+        <v>1.0369</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2421</v>
+        <v>0.2423</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1527</v>
+        <v>-0.1334</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0358</v>
+        <v>1.0369</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7652</v>
+        <v>1.6922</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7294</v>
+        <v>-0.6553</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7652</v>
+        <v>1.6922</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9532</v>
+        <v>0.9500999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7294</v>
+        <v>-0.6553</v>
       </c>
       <c r="K10" t="n">
         <v>139</v>
@@ -897,7 +897,7 @@
         <v>112</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2238</v>
+        <v>0.2948</v>
       </c>
       <c r="N10" t="n">
         <v>251</v>
@@ -906,93 +906,93 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9821</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2295</v>
+        <v>0.194</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1771</v>
+        <v>-0.2276</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9821</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7083</v>
+        <v>0.695</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2738</v>
+        <v>0.1351</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7083</v>
+        <v>0.695</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3825</v>
+        <v>0.3902</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2738</v>
+        <v>0.1351</v>
       </c>
       <c r="K11" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6563</v>
+        <v>0.5253</v>
       </c>
       <c r="N11" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.862</v>
+        <v>0.7967</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2015</v>
+        <v>0.1862</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2318</v>
+        <v>-0.2429</v>
       </c>
       <c r="E12" t="n">
-        <v>0.862</v>
+        <v>0.7967</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6924</v>
+        <v>0.5327</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1696</v>
+        <v>0.264</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6924</v>
+        <v>0.5327</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3739</v>
+        <v>0.2991</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1696</v>
+        <v>0.264</v>
       </c>
       <c r="K12" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="L12" t="n">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5435</v>
+        <v>0.5630999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4008</v>
+        <v>0.2977</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0696</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4418</v>
+        <v>-0.4702</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4008</v>
+        <v>0.2977</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4245</v>
+        <v>0.3163</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0237</v>
+        <v>-0.0186</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4245</v>
+        <v>0.3163</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2292</v>
+        <v>0.1776</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0237</v>
+        <v>-0.0186</v>
       </c>
       <c r="K13" t="n">
         <v>83</v>
@@ -1035,7 +1035,7 @@
         <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2055</v>
+        <v>0.159</v>
       </c>
       <c r="N13" t="n">
         <v>135</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.101</v>
+        <v>-0.0221</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0236</v>
+        <v>-0.0052</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5782</v>
+        <v>-0.6159</v>
       </c>
       <c r="E14" t="n">
-        <v>0.101</v>
+        <v>-0.0221</v>
       </c>
       <c r="F14" t="n">
-        <v>0.823</v>
+        <v>0.4868</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.722</v>
+        <v>-0.5089</v>
       </c>
       <c r="H14" t="n">
-        <v>0.823</v>
+        <v>0.4868</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4444</v>
+        <v>0.2733</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.722</v>
+        <v>-0.5089</v>
       </c>
       <c r="K14" t="n">
         <v>83</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2776</v>
+        <v>-0.2356</v>
       </c>
       <c r="N14" t="n">
         <v>135</v>
@@ -1090,35 +1090,35 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.0818</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0183</v>
+        <v>-0.0191</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5886</v>
+        <v>-0.6431</v>
       </c>
       <c r="E15" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.0818</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6211</v>
+        <v>0.6193</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6211</v>
+        <v>0.6193</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3354</v>
+        <v>0.3477</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>83</v>
@@ -1127,7 +1127,7 @@
         <v>52</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2074</v>
+        <v>-0.3533999999999999</v>
       </c>
       <c r="N15" t="n">
         <v>135</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.1049</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0158</v>
+        <v>-0.0245</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.655</v>
+        <v>-0.6536</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.1049</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7148</v>
+        <v>-0.6857</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6472</v>
+        <v>0.5808</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7148</v>
+        <v>-0.6857</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.386</v>
+        <v>-0.385</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6472</v>
+        <v>0.5808</v>
       </c>
       <c r="K16" t="n">
         <v>107</v>
@@ -1173,7 +1173,7 @@
         <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2612</v>
+        <v>0.1958</v>
       </c>
       <c r="N16" t="n">
         <v>159</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.1306</v>
+        <v>-0.1879</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0305</v>
+        <v>-0.0439</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6837</v>
+        <v>-0.6914</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1306</v>
+        <v>-0.1879</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1989</v>
+        <v>-0.239</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0683</v>
+        <v>0.0511</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1989</v>
+        <v>-0.239</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1074</v>
+        <v>-0.1342</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0683</v>
+        <v>0.0511</v>
       </c>
       <c r="K17" t="n">
         <v>83</v>
@@ -1219,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0391</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>135</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1.242</v>
+        <v>-1.1352</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.2903</v>
+        <v>-0.2653</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1896</v>
+        <v>-1.1229</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.242</v>
+        <v>-1.1352</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5137</v>
+        <v>-0.4568</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.6784</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5137</v>
+        <v>-0.4568</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2774</v>
+        <v>-0.2565</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.6784</v>
       </c>
       <c r="K18" t="n">
         <v>139</v>
@@ -1265,7 +1265,7 @@
         <v>112</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0057</v>
+        <v>-0.9349000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>251</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-1.3793</v>
+        <v>-1.181</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.3223</v>
+        <v>-0.276</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2521</v>
+        <v>-1.1438</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3793</v>
+        <v>-1.181</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6887</v>
+        <v>-1.5226</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3094</v>
+        <v>0.3416</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6887</v>
+        <v>-1.5226</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9119</v>
+        <v>-0.8549</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3094</v>
+        <v>0.3416</v>
       </c>
       <c r="K19" t="n">
         <v>107</v>
@@ -1311,7 +1311,7 @@
         <v>52</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6025</v>
+        <v>-0.5133</v>
       </c>
       <c r="N19" t="n">
         <v>159</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-1.4204</v>
+        <v>-1.2461</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.332</v>
+        <v>-0.2912</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2708</v>
+        <v>-1.1734</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4204</v>
+        <v>-1.2461</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4543</v>
+        <v>-1.2836</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0339</v>
+        <v>0.0375</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4543</v>
+        <v>-1.2836</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7853</v>
+        <v>-0.7207</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0339</v>
+        <v>0.0375</v>
       </c>
       <c r="K20" t="n">
         <v>107</v>
@@ -1357,7 +1357,7 @@
         <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7514</v>
+        <v>-0.6832</v>
       </c>
       <c r="N20" t="n">
         <v>159</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-2.5781</v>
+        <v>-2.2587</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.6025</v>
+        <v>-0.5279</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7978</v>
+        <v>-1.6347</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5781</v>
+        <v>-2.2587</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5772</v>
+        <v>-1.3192</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0009</v>
+        <v>-0.9395</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5772</v>
+        <v>-1.3192</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8517</v>
+        <v>-0.7407</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0009</v>
+        <v>-0.9395</v>
       </c>
       <c r="K21" t="n">
         <v>139</v>
@@ -1403,7 +1403,7 @@
         <v>112</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8526</v>
+        <v>-1.6802</v>
       </c>
       <c r="N21" t="n">
         <v>251</v>
@@ -1509,10 +1509,10 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9174</v>
+        <v>0.9008</v>
       </c>
       <c r="J2" t="n">
-        <v>24.7698</v>
+        <v>24.3216</v>
       </c>
     </row>
     <row r="3">
@@ -1549,10 +1549,10 @@
         <v>1.23</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6259</v>
+        <v>0.5894</v>
       </c>
       <c r="J3" t="n">
-        <v>16.8993</v>
+        <v>15.9138</v>
       </c>
     </row>
     <row r="4">
@@ -1589,10 +1589,10 @@
         <v>1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5596</v>
+        <v>0.5212</v>
       </c>
       <c r="J4" t="n">
-        <v>15.1092</v>
+        <v>14.0724</v>
       </c>
     </row>
     <row r="5">
@@ -1629,10 +1629,10 @@
         <v>0.87</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4405</v>
+        <v>-0.398</v>
       </c>
       <c r="J5" t="n">
-        <v>-11.8935</v>
+        <v>-10.746</v>
       </c>
     </row>
     <row r="6">
@@ -1669,10 +1669,10 @@
         <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4655</v>
+        <v>-0.4234</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.5685</v>
+        <v>-11.4318</v>
       </c>
     </row>
     <row r="7">
@@ -1709,10 +1709,10 @@
         <v>1.23</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5032</v>
+        <v>0.4459</v>
       </c>
       <c r="J7" t="n">
-        <v>13.5864</v>
+        <v>12.0393</v>
       </c>
     </row>
     <row r="8">
@@ -1749,10 +1749,10 @@
         <v>1.03</v>
       </c>
       <c r="I8" t="n">
-        <v>0.111</v>
+        <v>0.082</v>
       </c>
       <c r="J8" t="n">
-        <v>2.997</v>
+        <v>2.214</v>
       </c>
     </row>
     <row r="9">
@@ -1789,10 +1789,10 @@
         <v>0.91</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.13</v>
+        <v>-0.1122</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.51</v>
+        <v>-3.0294</v>
       </c>
     </row>
     <row r="10">
@@ -1829,10 +1829,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2361</v>
+        <v>-0.216</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.3747</v>
+        <v>-5.832</v>
       </c>
     </row>
     <row r="11">
@@ -1869,10 +1869,10 @@
         <v>0.68</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3597</v>
+        <v>-0.3454</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.7119</v>
+        <v>-9.325799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1909,10 +1909,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7821</v>
+        <v>0.754</v>
       </c>
       <c r="J12" t="n">
-        <v>21.8988</v>
+        <v>21.112</v>
       </c>
     </row>
     <row r="13">
@@ -1949,10 +1949,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5199</v>
+        <v>0.4797</v>
       </c>
       <c r="J13" t="n">
-        <v>14.5572</v>
+        <v>13.4316</v>
       </c>
     </row>
     <row r="14">
@@ -1989,10 +1989,10 @@
         <v>1.06</v>
       </c>
       <c r="I14" t="n">
-        <v>0.219</v>
+        <v>0.1868</v>
       </c>
       <c r="J14" t="n">
-        <v>6.132</v>
+        <v>5.2304</v>
       </c>
     </row>
     <row r="15">
@@ -2029,10 +2029,10 @@
         <v>0.97</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1496</v>
+        <v>-0.1188</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.1888</v>
+        <v>-3.3264</v>
       </c>
     </row>
     <row r="16">
@@ -2069,10 +2069,10 @@
         <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3842</v>
+        <v>-0.3413</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.7576</v>
+        <v>-9.5564</v>
       </c>
     </row>
     <row r="17">
@@ -2109,10 +2109,10 @@
         <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0823</v>
+        <v>0.0586</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3044</v>
+        <v>1.6408</v>
       </c>
     </row>
     <row r="18">
@@ -2149,10 +2149,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0074</v>
+        <v>0.0045</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2072</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="19">
@@ -2189,10 +2189,10 @@
         <v>0.96</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0564</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.932</v>
+        <v>-1.5792</v>
       </c>
     </row>
     <row r="20">
@@ -2229,10 +2229,10 @@
         <v>0.92</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.119</v>
+        <v>-0.1017</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.332</v>
+        <v>-2.8476</v>
       </c>
     </row>
     <row r="21">
@@ -2269,10 +2269,10 @@
         <v>0.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2468</v>
+        <v>-0.2269</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.9104</v>
+        <v>-6.3532</v>
       </c>
     </row>
     <row r="22">
@@ -2309,10 +2309,10 @@
         <v>1.06</v>
       </c>
       <c r="I22" t="n">
-        <v>0.207</v>
+        <v>0.1671</v>
       </c>
       <c r="J22" t="n">
-        <v>5.382</v>
+        <v>4.3446</v>
       </c>
     </row>
     <row r="23">
@@ -2349,10 +2349,10 @@
         <v>0.87</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1675</v>
+        <v>-0.1504</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.355</v>
+        <v>-3.9104</v>
       </c>
     </row>
     <row r="24">
@@ -2389,10 +2389,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2178</v>
+        <v>-0.1993</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.6628</v>
+        <v>-5.1818</v>
       </c>
     </row>
     <row r="25">
@@ -2429,10 +2429,10 @@
         <v>0.78</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2566</v>
+        <v>-0.238</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.6716</v>
+        <v>-6.188</v>
       </c>
     </row>
     <row r="26">
@@ -2469,10 +2469,10 @@
         <v>0.67</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3594</v>
+        <v>-0.3448</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.3444</v>
+        <v>-8.9648</v>
       </c>
     </row>
     <row r="27">
@@ -2509,10 +2509,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.8701</v>
       </c>
       <c r="J27" t="n">
-        <v>23.0776</v>
+        <v>22.6226</v>
       </c>
     </row>
     <row r="28">
@@ -2549,10 +2549,10 @@
         <v>1.27</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6886</v>
+        <v>0.6593</v>
       </c>
       <c r="J28" t="n">
-        <v>17.9036</v>
+        <v>17.1418</v>
       </c>
     </row>
     <row r="29">
@@ -2589,10 +2589,10 @@
         <v>1.27</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6886</v>
+        <v>0.6593</v>
       </c>
       <c r="J29" t="n">
-        <v>17.9036</v>
+        <v>17.1418</v>
       </c>
     </row>
     <row r="30">
@@ -2629,10 +2629,10 @@
         <v>1.12</v>
       </c>
       <c r="I30" t="n">
-        <v>0.358</v>
+        <v>0.3247</v>
       </c>
       <c r="J30" t="n">
-        <v>9.308</v>
+        <v>8.4422</v>
       </c>
     </row>
     <row r="31">
@@ -2669,10 +2669,10 @@
         <v>1.07</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2253</v>
+        <v>0.1959</v>
       </c>
       <c r="J31" t="n">
-        <v>5.8578</v>
+        <v>5.0934</v>
       </c>
     </row>
     <row r="32">
@@ -2709,10 +2709,10 @@
         <v>1.28</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5544</v>
+        <v>0.4946</v>
       </c>
       <c r="J32" t="n">
-        <v>16.632</v>
+        <v>14.838</v>
       </c>
     </row>
     <row r="33">
@@ -2749,10 +2749,10 @@
         <v>1.13</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3017</v>
+        <v>0.2518</v>
       </c>
       <c r="J33" t="n">
-        <v>9.051</v>
+        <v>7.554</v>
       </c>
     </row>
     <row r="34">
@@ -2789,10 +2789,10 @@
         <v>0.99</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0281</v>
+        <v>-0.02</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.843</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="35">
@@ -2829,10 +2829,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1026</v>
+        <v>-0.0851</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.078</v>
+        <v>-2.553</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>0.88</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1731</v>
+        <v>-0.1527</v>
       </c>
       <c r="J36" t="n">
-        <v>-5.193</v>
+        <v>-4.581</v>
       </c>
     </row>
     <row r="37">
@@ -2909,10 +2909,10 @@
         <v>1.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.957</v>
       </c>
       <c r="J37" t="n">
-        <v>28.986</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="38">
@@ -2949,10 +2949,10 @@
         <v>1.36</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8897</v>
+        <v>0.8706</v>
       </c>
       <c r="J38" t="n">
-        <v>26.691</v>
+        <v>26.118</v>
       </c>
     </row>
     <row r="39">
@@ -2989,10 +2989,10 @@
         <v>1.15</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4412</v>
+        <v>0.4032</v>
       </c>
       <c r="J39" t="n">
-        <v>13.236</v>
+        <v>12.096</v>
       </c>
     </row>
     <row r="40">
@@ -3029,10 +3029,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2554</v>
+        <v>-0.2166</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.662</v>
+        <v>-6.498</v>
       </c>
     </row>
     <row r="41">
@@ -3069,10 +3069,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5903</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.709</v>
+        <v>-16.587</v>
       </c>
     </row>
     <row r="42">
@@ -3109,10 +3109,10 @@
         <v>1.18</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3975</v>
+        <v>0.3413</v>
       </c>
       <c r="J42" t="n">
-        <v>11.5275</v>
+        <v>9.8977</v>
       </c>
     </row>
     <row r="43">
@@ -3149,10 +3149,10 @@
         <v>1.15</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3445</v>
+        <v>0.291</v>
       </c>
       <c r="J43" t="n">
-        <v>9.990500000000001</v>
+        <v>8.439</v>
       </c>
     </row>
     <row r="44">
@@ -3189,10 +3189,10 @@
         <v>1.01</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0427</v>
+        <v>0.0291</v>
       </c>
       <c r="J44" t="n">
-        <v>1.2383</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="45">
@@ -3229,10 +3229,10 @@
         <v>0.99</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0257</v>
+        <v>-0.0184</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.7453</v>
+        <v>-0.5336</v>
       </c>
     </row>
     <row r="46">
@@ -3269,10 +3269,10 @@
         <v>0.71</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3392</v>
+        <v>-0.3238</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.8368</v>
+        <v>-9.3902</v>
       </c>
     </row>
     <row r="47">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6721</v>
+        <v>0.6369</v>
       </c>
       <c r="J47" t="n">
-        <v>19.4909</v>
+        <v>18.4701</v>
       </c>
     </row>
     <row r="48">
@@ -3349,10 +3349,10 @@
         <v>1.17</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5119</v>
+        <v>0.4702</v>
       </c>
       <c r="J48" t="n">
-        <v>14.8451</v>
+        <v>13.6358</v>
       </c>
     </row>
     <row r="49">
@@ -3389,10 +3389,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.197</v>
+        <v>0.1636</v>
       </c>
       <c r="J49" t="n">
-        <v>5.713</v>
+        <v>4.7444</v>
       </c>
     </row>
     <row r="50">
@@ -3429,10 +3429,10 @@
         <v>0.83</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5209</v>
+        <v>-0.4792</v>
       </c>
       <c r="J50" t="n">
-        <v>-15.1061</v>
+        <v>-13.8968</v>
       </c>
     </row>
     <row r="51">
@@ -3469,10 +3469,10 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5911999999999999</v>
+        <v>-0.5521</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.1448</v>
+        <v>-16.0109</v>
       </c>
     </row>
     <row r="52">
@@ -3509,10 +3509,10 @@
         <v>1.26</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3733</v>
+        <v>0.3126</v>
       </c>
       <c r="J52" t="n">
-        <v>10.4524</v>
+        <v>8.752800000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3549,10 +3549,10 @@
         <v>1.17</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2659</v>
+        <v>0.2159</v>
       </c>
       <c r="J53" t="n">
-        <v>7.4452</v>
+        <v>6.0452</v>
       </c>
     </row>
     <row r="54">
@@ -3589,10 +3589,10 @@
         <v>1.15</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2411</v>
+        <v>0.1942</v>
       </c>
       <c r="J54" t="n">
-        <v>6.7508</v>
+        <v>5.4376</v>
       </c>
     </row>
     <row r="55">
@@ -3629,10 +3629,10 @@
         <v>1.12</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2022</v>
+        <v>0.1605</v>
       </c>
       <c r="J55" t="n">
-        <v>5.6616</v>
+        <v>4.494</v>
       </c>
     </row>
     <row r="56">
@@ -3669,10 +3669,10 @@
         <v>1.05</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0977</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>2.7356</v>
+        <v>2.0412</v>
       </c>
     </row>
     <row r="57">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I57" t="n">
-        <v>0.281</v>
+        <v>0.2678</v>
       </c>
       <c r="J57" t="n">
-        <v>7.868</v>
+        <v>7.4984</v>
       </c>
     </row>
     <row r="58">
@@ -3749,10 +3749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0953</v>
+        <v>-0.0798</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.6684</v>
+        <v>-2.2344</v>
       </c>
     </row>
     <row r="59">
@@ -3789,10 +3789,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1194</v>
+        <v>-0.102</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.3432</v>
+        <v>-2.856</v>
       </c>
     </row>
     <row r="60">
@@ -3829,10 +3829,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1424</v>
+        <v>-0.1237</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.9872</v>
+        <v>-3.4636</v>
       </c>
     </row>
     <row r="61">
@@ -3869,10 +3869,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2274</v>
+        <v>-0.2071</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.3672</v>
+        <v>-5.7988</v>
       </c>
     </row>
     <row r="62">
@@ -3909,10 +3909,10 @@
         <v>1.04</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1358</v>
+        <v>0.1027</v>
       </c>
       <c r="J62" t="n">
-        <v>3.5308</v>
+        <v>2.6702</v>
       </c>
     </row>
     <row r="63">
@@ -3949,10 +3949,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0527</v>
+        <v>0.0355</v>
       </c>
       <c r="J63" t="n">
-        <v>1.3702</v>
+        <v>0.923</v>
       </c>
     </row>
     <row r="64">
@@ -3989,10 +3989,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1068</v>
+        <v>-0.0906</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.7768</v>
+        <v>-2.3556</v>
       </c>
     </row>
     <row r="65">
@@ -4029,10 +4029,10 @@
         <v>0.9</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1415</v>
+        <v>-0.123</v>
       </c>
       <c r="J65" t="n">
-        <v>-3.679</v>
+        <v>-3.198</v>
       </c>
     </row>
     <row r="66">
@@ -4069,10 +4069,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2561</v>
+        <v>-0.2364</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.6586</v>
+        <v>-6.1464</v>
       </c>
     </row>
     <row r="67">
@@ -4109,10 +4109,10 @@
         <v>1.47</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0838</v>
+        <v>1.0945</v>
       </c>
       <c r="J67" t="n">
-        <v>28.1788</v>
+        <v>28.457</v>
       </c>
     </row>
     <row r="68">
@@ -4149,10 +4149,10 @@
         <v>1.24</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6466</v>
+        <v>0.6111</v>
       </c>
       <c r="J68" t="n">
-        <v>16.8116</v>
+        <v>15.8886</v>
       </c>
     </row>
     <row r="69">
@@ -4189,10 +4189,10 @@
         <v>1.24</v>
       </c>
       <c r="I69" t="n">
-        <v>0.6466</v>
+        <v>0.6111</v>
       </c>
       <c r="J69" t="n">
-        <v>16.8116</v>
+        <v>15.8886</v>
       </c>
     </row>
     <row r="70">
@@ -4229,10 +4229,10 @@
         <v>0.86</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4663</v>
+        <v>-0.4242</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.1238</v>
+        <v>-11.0292</v>
       </c>
     </row>
     <row r="71">
@@ -4269,10 +4269,10 @@
         <v>0.74</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7439</v>
+        <v>-0.7161</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.3414</v>
+        <v>-18.6186</v>
       </c>
     </row>
     <row r="72">
@@ -4309,10 +4309,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1975</v>
+        <v>0.1573</v>
       </c>
       <c r="J72" t="n">
-        <v>5.3325</v>
+        <v>4.2471</v>
       </c>
     </row>
     <row r="73">
@@ -4349,10 +4349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0895</v>
+        <v>-0.0759</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.4165</v>
+        <v>-2.0493</v>
       </c>
     </row>
     <row r="74">
@@ -4389,10 +4389,10 @@
         <v>0.88</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1594</v>
+        <v>-0.1417</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.3038</v>
+        <v>-3.8259</v>
       </c>
     </row>
     <row r="75">
@@ -4429,10 +4429,10 @@
         <v>0.8</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2403</v>
+        <v>-0.2209</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.4881</v>
+        <v>-5.9643</v>
       </c>
     </row>
     <row r="76">
@@ -4469,10 +4469,10 @@
         <v>0.68</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3537</v>
+        <v>-0.3387</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.549899999999999</v>
+        <v>-9.1449</v>
       </c>
     </row>
     <row r="77">
@@ -4509,10 +4509,10 @@
         <v>1.67</v>
       </c>
       <c r="I77" t="n">
-        <v>1.331</v>
+        <v>1.3534</v>
       </c>
       <c r="J77" t="n">
-        <v>35.937</v>
+        <v>36.5418</v>
       </c>
     </row>
     <row r="78">
@@ -4549,10 +4549,10 @@
         <v>1.29</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7319</v>
+        <v>0.7039</v>
       </c>
       <c r="J78" t="n">
-        <v>19.7613</v>
+        <v>19.0053</v>
       </c>
     </row>
     <row r="79">
@@ -4589,10 +4589,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.4671</v>
       </c>
       <c r="J79" t="n">
-        <v>13.5405</v>
+        <v>12.6117</v>
       </c>
     </row>
     <row r="80">
@@ -4629,10 +4629,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.238</v>
+        <v>-0.2015</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.426</v>
+        <v>-5.4405</v>
       </c>
     </row>
     <row r="81">
@@ -4669,10 +4669,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2978</v>
+        <v>-0.2585</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.0406</v>
+        <v>-6.9795</v>
       </c>
     </row>
     <row r="82">
@@ -4709,10 +4709,10 @@
         <v>0.76</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.2654</v>
+        <v>-0.2505</v>
       </c>
       <c r="J82" t="n">
-        <v>-6.3696</v>
+        <v>-6.012</v>
       </c>
     </row>
     <row r="83">
@@ -4749,10 +4749,10 @@
         <v>0.75</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.2749</v>
+        <v>-0.2599</v>
       </c>
       <c r="J83" t="n">
-        <v>-6.5976</v>
+        <v>-6.2376</v>
       </c>
     </row>
     <row r="84">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2841</v>
+        <v>-0.2692</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.8184</v>
+        <v>-6.4608</v>
       </c>
     </row>
     <row r="85">
@@ -4829,10 +4829,10 @@
         <v>0.71</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3105</v>
+        <v>-0.2958</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.452</v>
+        <v>-7.0992</v>
       </c>
     </row>
     <row r="86">
@@ -4869,10 +4869,10 @@
         <v>0.66</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3552</v>
+        <v>-0.3417</v>
       </c>
       <c r="J86" t="n">
-        <v>-8.524800000000001</v>
+        <v>-8.200799999999999</v>
       </c>
     </row>
     <row r="87">
@@ -4909,10 +4909,10 @@
         <v>1.59</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1934</v>
+        <v>1.209</v>
       </c>
       <c r="J87" t="n">
-        <v>28.6416</v>
+        <v>29.016</v>
       </c>
     </row>
     <row r="88">
@@ -4949,10 +4949,10 @@
         <v>1.46</v>
       </c>
       <c r="I88" t="n">
-        <v>1.0192</v>
+        <v>1.0239</v>
       </c>
       <c r="J88" t="n">
-        <v>24.4608</v>
+        <v>24.5736</v>
       </c>
     </row>
     <row r="89">
@@ -4989,10 +4989,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6717</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>16.1208</v>
+        <v>15.5688</v>
       </c>
     </row>
     <row r="90">
@@ -5029,10 +5029,10 @@
         <v>1.26</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6512</v>
+        <v>0.6272</v>
       </c>
       <c r="J90" t="n">
-        <v>15.6288</v>
+        <v>15.0528</v>
       </c>
     </row>
     <row r="91">
@@ -5069,10 +5069,10 @@
         <v>1.24</v>
       </c>
       <c r="I91" t="n">
-        <v>0.6094000000000001</v>
+        <v>0.5837</v>
       </c>
       <c r="J91" t="n">
-        <v>14.6256</v>
+        <v>14.0088</v>
       </c>
     </row>
     <row r="92">
@@ -5109,10 +5109,10 @@
         <v>1.15</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3651</v>
+        <v>0.3112</v>
       </c>
       <c r="J92" t="n">
-        <v>10.2228</v>
+        <v>8.7136</v>
       </c>
     </row>
     <row r="93">
@@ -5149,10 +5149,10 @@
         <v>1.07</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2069</v>
+        <v>0.1647</v>
       </c>
       <c r="J93" t="n">
-        <v>5.7932</v>
+        <v>4.6116</v>
       </c>
     </row>
     <row r="94">
@@ -5189,10 +5189,10 @@
         <v>0.82</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2251</v>
+        <v>-0.205</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.3028</v>
+        <v>-5.74</v>
       </c>
     </row>
     <row r="95">
@@ -5229,10 +5229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2351</v>
+        <v>-0.2151</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.5828</v>
+        <v>-6.0228</v>
       </c>
     </row>
     <row r="96">
@@ -5269,10 +5269,10 @@
         <v>0.76</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.284</v>
+        <v>-0.2652</v>
       </c>
       <c r="J96" t="n">
-        <v>-7.952</v>
+        <v>-7.4256</v>
       </c>
     </row>
     <row r="97">
@@ -5309,10 +5309,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9587</v>
+        <v>0.9449</v>
       </c>
       <c r="J97" t="n">
-        <v>26.8436</v>
+        <v>26.4572</v>
       </c>
     </row>
     <row r="98">
@@ -5349,10 +5349,10 @@
         <v>1.2</v>
       </c>
       <c r="I98" t="n">
-        <v>0.5179</v>
+        <v>0.5079</v>
       </c>
       <c r="J98" t="n">
-        <v>14.5012</v>
+        <v>14.2212</v>
       </c>
     </row>
     <row r="99">
@@ -5389,10 +5389,10 @@
         <v>1.13</v>
       </c>
       <c r="I99" t="n">
-        <v>0.387</v>
+        <v>0.3525</v>
       </c>
       <c r="J99" t="n">
-        <v>10.836</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -5429,10 +5429,10 @@
         <v>1.07</v>
       </c>
       <c r="I100" t="n">
-        <v>0.23</v>
+        <v>0.2002</v>
       </c>
       <c r="J100" t="n">
-        <v>6.44</v>
+        <v>5.6056</v>
       </c>
     </row>
     <row r="101">
@@ -5469,10 +5469,10 @@
         <v>1.06</v>
       </c>
       <c r="I101" t="n">
-        <v>0.201</v>
+        <v>0.1728</v>
       </c>
       <c r="J101" t="n">
-        <v>5.628</v>
+        <v>4.8384</v>
       </c>
     </row>
     <row r="102">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4784</v>
+        <v>0.4361</v>
       </c>
       <c r="J102" t="n">
-        <v>13.8736</v>
+        <v>12.6469</v>
       </c>
     </row>
     <row r="103">
@@ -5549,10 +5549,10 @@
         <v>0.92</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1175</v>
+        <v>-0.1011</v>
       </c>
       <c r="J103" t="n">
-        <v>-3.4075</v>
+        <v>-2.9319</v>
       </c>
     </row>
     <row r="104">
@@ -5589,10 +5589,10 @@
         <v>0.91</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1288</v>
+        <v>-0.1117</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.7352</v>
+        <v>-3.2393</v>
       </c>
     </row>
     <row r="105">
@@ -5629,10 +5629,10 @@
         <v>0.89</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1509</v>
+        <v>-0.1325</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.3761</v>
+        <v>-3.8425</v>
       </c>
     </row>
     <row r="106">
@@ -5669,10 +5669,10 @@
         <v>0.62</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4118</v>
+        <v>-0.4019</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.9422</v>
+        <v>-11.6551</v>
       </c>
     </row>
     <row r="107">
@@ -5709,10 +5709,10 @@
         <v>1.46</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9049</v>
+        <v>0.8899</v>
       </c>
       <c r="J107" t="n">
-        <v>26.2421</v>
+        <v>25.8071</v>
       </c>
     </row>
     <row r="108">
@@ -5749,10 +5749,10 @@
         <v>1.28</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6432</v>
+        <v>0.6308</v>
       </c>
       <c r="J108" t="n">
-        <v>18.6528</v>
+        <v>18.2932</v>
       </c>
     </row>
     <row r="109">
@@ -5789,10 +5789,10 @@
         <v>1.12</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3636</v>
+        <v>0.3292</v>
       </c>
       <c r="J109" t="n">
-        <v>10.5444</v>
+        <v>9.546799999999999</v>
       </c>
     </row>
     <row r="110">
@@ -5829,10 +5829,10 @@
         <v>1.05</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1722</v>
+        <v>0.1459</v>
       </c>
       <c r="J110" t="n">
-        <v>4.9938</v>
+        <v>4.2311</v>
       </c>
     </row>
     <row r="111">
@@ -5869,10 +5869,10 @@
         <v>1.01</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0291</v>
+        <v>0.0192</v>
       </c>
       <c r="J111" t="n">
-        <v>0.8439</v>
+        <v>0.5568</v>
       </c>
     </row>
     <row r="112">
@@ -5909,10 +5909,10 @@
         <v>1.33</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6051</v>
+        <v>0.579</v>
       </c>
       <c r="J112" t="n">
-        <v>17.5479</v>
+        <v>16.791</v>
       </c>
     </row>
     <row r="113">
@@ -5949,10 +5949,10 @@
         <v>0.98</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0391</v>
+        <v>-0.0305</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.1339</v>
+        <v>-0.8845</v>
       </c>
     </row>
     <row r="114">
@@ -5989,10 +5989,10 @@
         <v>0.97</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.0547</v>
+        <v>-0.0438</v>
       </c>
       <c r="J114" t="n">
-        <v>-1.5863</v>
+        <v>-1.2702</v>
       </c>
     </row>
     <row r="115">
@@ -6029,10 +6029,10 @@
         <v>0.87</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1749</v>
+        <v>-0.155</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.0721</v>
+        <v>-4.495</v>
       </c>
     </row>
     <row r="116">
@@ -6069,10 +6069,10 @@
         <v>0.55</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4756</v>
+        <v>-0.4732</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.7924</v>
+        <v>-13.7228</v>
       </c>
     </row>
     <row r="117">
@@ -6109,10 +6109,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9201</v>
       </c>
       <c r="J117" t="n">
-        <v>27.086</v>
+        <v>26.6829</v>
       </c>
     </row>
     <row r="118">
@@ -6149,10 +6149,10 @@
         <v>1.16</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4585</v>
+        <v>0.4272</v>
       </c>
       <c r="J118" t="n">
-        <v>13.2965</v>
+        <v>12.3888</v>
       </c>
     </row>
     <row r="119">
@@ -6189,10 +6189,10 @@
         <v>1.08</v>
       </c>
       <c r="I119" t="n">
-        <v>0.2695</v>
+        <v>0.2359</v>
       </c>
       <c r="J119" t="n">
-        <v>7.8155</v>
+        <v>6.8411</v>
       </c>
     </row>
     <row r="120">
@@ -6229,10 +6229,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.157</v>
+        <v>-0.1256</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.553</v>
+        <v>-3.6424</v>
       </c>
     </row>
     <row r="121">
@@ -6269,10 +6269,10 @@
         <v>0.92</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3109</v>
+        <v>-0.2697</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.0161</v>
+        <v>-7.8213</v>
       </c>
     </row>
     <row r="122">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1074</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>2.4702</v>
+        <v>1.8768</v>
       </c>
     </row>
     <row r="123">
@@ -6349,10 +6349,10 @@
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.031</v>
+        <v>0.0252</v>
       </c>
       <c r="J123" t="n">
-        <v>0.713</v>
+        <v>0.5796</v>
       </c>
     </row>
     <row r="124">
@@ -6389,10 +6389,10 @@
         <v>0.79</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2464</v>
+        <v>-0.2279</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.6672</v>
+        <v>-5.2417</v>
       </c>
     </row>
     <row r="125">
@@ -6429,10 +6429,10 @@
         <v>0.7</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3313</v>
+        <v>-0.315</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.6199</v>
+        <v>-7.245</v>
       </c>
     </row>
     <row r="126">
@@ -6469,10 +6469,10 @@
         <v>0.66</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3679</v>
+        <v>-0.3539</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.4617</v>
+        <v>-8.139699999999999</v>
       </c>
     </row>
     <row r="127">
@@ -6509,10 +6509,10 @@
         <v>1.55</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0138</v>
+        <v>1.0017</v>
       </c>
       <c r="J127" t="n">
-        <v>23.3174</v>
+        <v>23.0391</v>
       </c>
     </row>
     <row r="128">
@@ -6549,10 +6549,10 @@
         <v>1.27</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6203</v>
+        <v>0.6113</v>
       </c>
       <c r="J128" t="n">
-        <v>14.2669</v>
+        <v>14.0599</v>
       </c>
     </row>
     <row r="129">
@@ -6589,10 +6589,10 @@
         <v>1.25</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5908</v>
+        <v>0.5833</v>
       </c>
       <c r="J129" t="n">
-        <v>13.5884</v>
+        <v>13.4159</v>
       </c>
     </row>
     <row r="130">
@@ -6629,10 +6629,10 @@
         <v>1.13</v>
       </c>
       <c r="I130" t="n">
-        <v>0.3777</v>
+        <v>0.3449</v>
       </c>
       <c r="J130" t="n">
-        <v>8.687099999999999</v>
+        <v>7.9327</v>
       </c>
     </row>
     <row r="131">
@@ -6669,10 +6669,10 @@
         <v>1.06</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1909</v>
+        <v>0.1631</v>
       </c>
       <c r="J131" t="n">
-        <v>4.3907</v>
+        <v>3.7513</v>
       </c>
     </row>
   </sheetData>
